--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>Practitioner.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
